--- a/data/raw/inventory/Week 26/White_Mulberry/Inventory Snapshot.xlsx
+++ b/data/raw/inventory/Week 26/White_Mulberry/Inventory Snapshot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 26\White_Mulberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C71DDA2-1E04-485A-84A4-B5CFAAA284FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B5C213-CD26-4A52-AF68-DE9B1F4E248F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -210,9 +210,6 @@
     <t>White Mulberry</t>
   </si>
   <si>
-    <t>Pipeline</t>
-  </si>
-  <si>
     <t>1P</t>
   </si>
   <si>
@@ -238,6 +235,9 @@
   </si>
   <si>
     <t>YNT</t>
+  </si>
+  <si>
+    <t>Open Order</t>
   </si>
 </sst>
 </file>
@@ -895,7 +895,7 @@
         <v>5</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -909,7 +909,7 @@
         <v>11</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -923,7 +923,7 @@
         <v>9</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -937,7 +937,7 @@
         <v>10</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -951,7 +951,7 @@
         <v>27</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -965,7 +965,7 @@
         <v>65</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -979,7 +979,7 @@
         <v>108</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -993,7 +993,7 @@
         <v>46</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1010,7 +1010,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1027,7 +1027,7 @@
         <v>15</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1044,15 +1044,15 @@
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>56</v>
@@ -1061,7 +1061,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1078,7 +1078,7 @@
         <v>439</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1095,7 +1095,7 @@
         <v>351</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1112,7 +1112,7 @@
         <v>579</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1129,7 +1129,7 @@
         <v>90</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1146,7 +1146,7 @@
         <v>15</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1163,7 +1163,7 @@
         <v>401</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1180,7 +1180,7 @@
         <v>281</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1197,7 +1197,7 @@
         <v>4</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1214,7 +1214,7 @@
         <v>202</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1231,7 +1231,7 @@
         <v>4</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1248,15 +1248,15 @@
         <v>18</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>56</v>
@@ -1265,7 +1265,7 @@
         <v>18</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1282,7 +1282,7 @@
         <v>112</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1299,7 +1299,7 @@
         <v>542</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1316,7 +1316,7 @@
         <v>6</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1333,7 +1333,7 @@
         <v>62</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1341,7 +1341,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>56</v>
@@ -1350,7 +1350,7 @@
         <v>685</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1367,7 +1367,7 @@
         <v>610</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1384,7 +1384,7 @@
         <v>4</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1401,7 +1401,7 @@
         <v>2</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1418,7 +1418,7 @@
         <v>3</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1435,7 +1435,7 @@
         <v>4</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1452,7 +1452,7 @@
         <v>5</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1469,7 +1469,7 @@
         <v>5</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K37" s="11"/>
     </row>
@@ -1487,7 +1487,7 @@
         <v>4</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K38" s="11"/>
     </row>
@@ -1505,7 +1505,7 @@
         <v>3</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K39" s="11"/>
     </row>
@@ -1523,7 +1523,7 @@
         <v>2</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K40" s="11"/>
     </row>
@@ -1541,7 +1541,7 @@
         <v>1000</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="K41" s="7"/>
     </row>
@@ -1559,36 +1559,36 @@
         <v>1000</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="K42" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L42" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A10:A31">
+    <cfRule type="duplicateValues" dxfId="9" priority="2204"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A37:A40">
+    <cfRule type="duplicateValues" dxfId="8" priority="2201"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A41:A42">
+    <cfRule type="duplicateValues" dxfId="7" priority="2199"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="9" priority="1919"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1919"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="8" priority="2130"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="2131" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2130"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2131" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="6" priority="1917"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1918" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1917"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1918" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="4" priority="1915"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1916" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A41:A42">
-    <cfRule type="duplicateValues" dxfId="2" priority="2199"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A37:A40">
-    <cfRule type="duplicateValues" dxfId="1" priority="2201"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A10:A31">
-    <cfRule type="duplicateValues" dxfId="0" priority="2204"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1915"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1916" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
